--- a/results/ticketInfo.xlsx
+++ b/results/ticketInfo.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2330" uniqueCount="944">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2374" uniqueCount="954">
   <si>
     <t>城市</t>
   </si>
@@ -2846,6 +2846,36 @@
   </si>
   <si>
     <t>23:05</t>
+  </si>
+  <si>
+    <t>2026-09-03</t>
+  </si>
+  <si>
+    <t>2026-09-10</t>
+  </si>
+  <si>
+    <t>09月03日 17:30</t>
+  </si>
+  <si>
+    <t>09月03日 20:05</t>
+  </si>
+  <si>
+    <t>09月10日 21:35</t>
+  </si>
+  <si>
+    <t>09月11日 00:10</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t>09月10日 06:50</t>
+  </si>
+  <si>
+    <t>09月10日 08:55</t>
+  </si>
+  <si>
+    <t>18:05</t>
   </si>
 </sst>
 </file>
@@ -3231,7 +3261,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L220"/>
+  <dimension ref="A1:L225"/>
   <sheetFormatPr defaultRowHeight="16.8" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
   <cols>
     <col min="1" max="12" width="15" customWidth="1"/>
@@ -11594,6 +11624,193 @@
         <v>18</v>
       </c>
     </row>
+    <row r="221" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>51</v>
+      </c>
+      <c r="B221">
+        <v>680</v>
+      </c>
+      <c r="C221" t="s">
+        <v>944</v>
+      </c>
+      <c r="D221" t="s">
+        <v>945</v>
+      </c>
+      <c r="E221" t="s">
+        <v>528</v>
+      </c>
+      <c r="F221" t="s">
+        <v>144</v>
+      </c>
+      <c r="G221">
+        <v>340</v>
+      </c>
+      <c r="H221" t="s">
+        <v>18</v>
+      </c>
+      <c r="I221" t="s">
+        <v>938</v>
+      </c>
+      <c r="J221" t="s">
+        <v>330</v>
+      </c>
+      <c r="K221">
+        <v>340</v>
+      </c>
+      <c r="L221" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="222" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>173</v>
+      </c>
+      <c r="B222">
+        <v>658</v>
+      </c>
+      <c r="C222" t="s">
+        <v>944</v>
+      </c>
+      <c r="D222" t="s">
+        <v>945</v>
+      </c>
+      <c r="E222" t="s">
+        <v>887</v>
+      </c>
+      <c r="F222" t="s">
+        <v>888</v>
+      </c>
+      <c r="G222">
+        <v>368</v>
+      </c>
+      <c r="H222" t="s">
+        <v>127</v>
+      </c>
+      <c r="I222" t="s">
+        <v>38</v>
+      </c>
+      <c r="J222" t="s">
+        <v>904</v>
+      </c>
+      <c r="K222">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="223" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>152</v>
+      </c>
+      <c r="B223">
+        <v>1457</v>
+      </c>
+      <c r="C223" t="s">
+        <v>944</v>
+      </c>
+      <c r="D223" t="s">
+        <v>945</v>
+      </c>
+      <c r="E223" t="s">
+        <v>946</v>
+      </c>
+      <c r="F223" t="s">
+        <v>947</v>
+      </c>
+      <c r="G223">
+        <v>847</v>
+      </c>
+      <c r="H223" t="s">
+        <v>156</v>
+      </c>
+      <c r="I223" t="s">
+        <v>948</v>
+      </c>
+      <c r="J223" t="s">
+        <v>949</v>
+      </c>
+      <c r="K223">
+        <v>610</v>
+      </c>
+      <c r="L223" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="224" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>525</v>
+      </c>
+      <c r="B224">
+        <v>1270</v>
+      </c>
+      <c r="C224" t="s">
+        <v>944</v>
+      </c>
+      <c r="D224" t="s">
+        <v>945</v>
+      </c>
+      <c r="E224" t="s">
+        <v>929</v>
+      </c>
+      <c r="F224" t="s">
+        <v>950</v>
+      </c>
+      <c r="G224">
+        <v>700</v>
+      </c>
+      <c r="H224" t="s">
+        <v>184</v>
+      </c>
+      <c r="I224" t="s">
+        <v>951</v>
+      </c>
+      <c r="J224" t="s">
+        <v>952</v>
+      </c>
+      <c r="K224">
+        <v>570</v>
+      </c>
+      <c r="L224" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="225" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>12</v>
+      </c>
+      <c r="B225">
+        <v>540</v>
+      </c>
+      <c r="C225" t="s">
+        <v>944</v>
+      </c>
+      <c r="D225" t="s">
+        <v>945</v>
+      </c>
+      <c r="E225" t="s">
+        <v>263</v>
+      </c>
+      <c r="F225" t="s">
+        <v>953</v>
+      </c>
+      <c r="G225">
+        <v>240</v>
+      </c>
+      <c r="H225" t="s">
+        <v>18</v>
+      </c>
+      <c r="I225" t="s">
+        <v>175</v>
+      </c>
+      <c r="J225" t="s">
+        <v>195</v>
+      </c>
+      <c r="K225">
+        <v>300</v>
+      </c>
+      <c r="L225" t="s">
+        <v>18</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
